--- a/output-app/Neraca, RL, Arus Kas, ekuitas & Rincian 2026.xlsx
+++ b/output-app/Neraca, RL, Arus Kas, ekuitas & Rincian 2026.xlsx
@@ -1052,8 +1052,8 @@
       <c r="D27" t="str">
         <v/>
       </c>
-      <c r="E27" t="str">
-        <v/>
+      <c r="E27">
+        <v>200000</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1122,7 +1122,7 @@
         <v/>
       </c>
       <c r="E30">
-        <v>1085400</v>
+        <v>885400</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
       <c r="G11">
-        <v>2230800</v>
+        <v>1905800</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -1562,7 +1562,7 @@
         <v/>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>125644</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1848,7 +1848,7 @@
         <v/>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
         <v/>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1978,7 +1978,7 @@
         <v/>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>21696230644.28</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -2030,7 +2030,7 @@
         <v/>
       </c>
       <c r="G34">
-        <v>1085400</v>
+        <v>885400</v>
       </c>
       <c r="H34" t="str">
         <v/>

--- a/output-app/Neraca, RL, Arus Kas, ekuitas & Rincian 2026.xlsx
+++ b/output-app/Neraca, RL, Arus Kas, ekuitas & Rincian 2026.xlsx
@@ -35,7 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
@@ -45,6 +45,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -711,7 +712,7 @@
         <v/>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -872,7 +873,7 @@
         <v/>
       </c>
       <c r="F19">
-        <v>1085400</v>
+        <v>2532600</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -984,7 +985,7 @@
         <v/>
       </c>
       <c r="E24">
-        <v>1085400</v>
+        <v>3032600</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1053,7 +1054,7 @@
         <v/>
       </c>
       <c r="E27">
-        <v>200000</v>
+        <v>800000</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1076,7 +1077,7 @@
         <v/>
       </c>
       <c r="E28">
-        <v>200000</v>
+        <v>800000</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1122,7 +1123,7 @@
         <v/>
       </c>
       <c r="E30">
-        <v>885400</v>
+        <v>2232600</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1432,7 +1433,7 @@
         <v/>
       </c>
       <c r="G11">
-        <v>1905800</v>
+        <v>4405200</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -1484,7 +1485,7 @@
         <v/>
       </c>
       <c r="G13">
-        <v>-1145400</v>
+        <v>-2672600</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -1562,7 +1563,7 @@
         <v/>
       </c>
       <c r="G16">
-        <v>125644</v>
+        <v>502576</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1848,7 +1849,7 @@
         <v/>
       </c>
       <c r="G27">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1874,7 +1875,7 @@
         <v/>
       </c>
       <c r="G28">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1978,7 +1979,7 @@
         <v/>
       </c>
       <c r="G32">
-        <v>21696230644.28</v>
+        <v>86784922577.11</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -2030,7 +2031,7 @@
         <v/>
       </c>
       <c r="G34">
-        <v>885400</v>
+        <v>2232600</v>
       </c>
       <c r="H34" t="str">
         <v/>

--- a/output-app/Neraca, RL, Arus Kas, ekuitas & Rincian 2026.xlsx
+++ b/output-app/Neraca, RL, Arus Kas, ekuitas & Rincian 2026.xlsx
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="F12">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="F19">
-        <v>2532600</v>
+        <v>723600</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -985,7 +985,7 @@
         <v/>
       </c>
       <c r="E24">
-        <v>3032600</v>
+        <v>723600</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="E27">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1077,7 +1077,7 @@
         <v/>
       </c>
       <c r="E28">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v/>
       </c>
       <c r="E30">
-        <v>2232600</v>
+        <v>323600</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="G11">
-        <v>4405200</v>
+        <v>837200</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -1485,7 +1485,7 @@
         <v/>
       </c>
       <c r="G13">
-        <v>-2672600</v>
+        <v>-763600</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -1563,7 +1563,7 @@
         <v/>
       </c>
       <c r="G16">
-        <v>502576</v>
+        <v>251288</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1849,7 +1849,7 @@
         <v/>
       </c>
       <c r="G27">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="G28">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1979,7 +1979,7 @@
         <v/>
       </c>
       <c r="G32">
-        <v>86784922577.11</v>
+        <v>43392461288.55</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -2031,7 +2031,7 @@
         <v/>
       </c>
       <c r="G34">
-        <v>2232600</v>
+        <v>323600</v>
       </c>
       <c r="H34" t="str">
         <v/>
